--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -413,410 +413,393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Radius</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17.28716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.46745</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.7379</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.85278</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.83486</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.86803</v>
+        <v>17.16803</v>
       </c>
       <c r="D3" t="n">
-        <v>17.06014</v>
+        <v>16.75954</v>
       </c>
       <c r="E3" t="n">
-        <v>17.23632</v>
+        <v>16.89294</v>
       </c>
       <c r="F3" t="n">
-        <v>43.29325</v>
+        <v>42.74486</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05067</v>
+        <v>0.0502</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83635</v>
+        <v>1.81307</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.78</v>
+        <v>16.72506</v>
       </c>
       <c r="D4" t="n">
-        <v>16.94376</v>
+        <v>16.63683</v>
       </c>
       <c r="E4" t="n">
-        <v>16.83876</v>
+        <v>16.72382</v>
       </c>
       <c r="F4" t="n">
-        <v>42.74016</v>
+        <v>42.94742</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04938</v>
+        <v>0.05021</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83161</v>
+        <v>1.8252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.71114</v>
+        <v>17.14332</v>
       </c>
       <c r="D5" t="n">
-        <v>16.71249</v>
+        <v>16.91247</v>
       </c>
       <c r="E5" t="n">
-        <v>16.76963</v>
+        <v>17.04477</v>
       </c>
       <c r="F5" t="n">
-        <v>42.69177</v>
+        <v>43.19051</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05105</v>
+        <v>0.04937</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8078</v>
+        <v>1.8467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.28716</v>
+        <v>17.00253</v>
       </c>
       <c r="D6" t="n">
-        <v>16.7379</v>
+        <v>16.52429</v>
       </c>
       <c r="E6" t="n">
-        <v>16.46745</v>
+        <v>16.7275</v>
       </c>
       <c r="F6" t="n">
-        <v>42.85278</v>
+        <v>42.83685</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0505</v>
+        <v>0.05019</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83486</v>
+        <v>1.85026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.16803</v>
+        <v>16.89518</v>
       </c>
       <c r="D7" t="n">
-        <v>16.89294</v>
+        <v>16.76059</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75954</v>
+        <v>16.78908</v>
       </c>
       <c r="F7" t="n">
-        <v>42.74486</v>
+        <v>43.42712</v>
       </c>
       <c r="G7" t="n">
         <v>0.0502</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81307</v>
+        <v>1.81093</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.72506</v>
+        <v>17.06124</v>
       </c>
       <c r="D8" t="n">
-        <v>16.72382</v>
+        <v>16.79784</v>
       </c>
       <c r="E8" t="n">
-        <v>16.63683</v>
+        <v>16.94246</v>
       </c>
       <c r="F8" t="n">
-        <v>42.94742</v>
+        <v>42.74526</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05021</v>
+        <v>0.05078</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8252</v>
+        <v>1.86392</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.04477</v>
+        <v>17.00475</v>
       </c>
       <c r="D9" t="n">
-        <v>16.91247</v>
+        <v>16.61629</v>
       </c>
       <c r="E9" t="n">
-        <v>17.14332</v>
+        <v>16.81624</v>
       </c>
       <c r="F9" t="n">
-        <v>43.19051</v>
+        <v>44.18991</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04937</v>
+        <v>0.05132</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8467</v>
+        <v>1.8468</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.00253</v>
+        <v>16.87681</v>
       </c>
       <c r="D10" t="n">
-        <v>16.52429</v>
+        <v>16.70423</v>
       </c>
       <c r="E10" t="n">
-        <v>16.7275</v>
+        <v>16.82738</v>
       </c>
       <c r="F10" t="n">
-        <v>42.83685</v>
+        <v>44.23243</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05019</v>
+        <v>0.05172</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85026</v>
+        <v>1.85053</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.76059</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.78908</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.89518</v>
-      </c>
-      <c r="F11" t="n">
-        <v>43.42712</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0502</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.81093</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.60336</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.13726</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.61238</v>
+        <v>0.59631</v>
       </c>
       <c r="D13" t="n">
-        <v>1.12668</v>
+        <v>1.13187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.62041</v>
+        <v>0.61211</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11952</v>
+        <v>1.1399</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.60933</v>
+        <v>0.6096200000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13906</v>
+        <v>1.12346</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60782</v>
+        <v>0.6039</v>
       </c>
       <c r="D16" t="n">
-        <v>1.11451</v>
+        <v>1.11764</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.61835</v>
+        <v>0.61</v>
       </c>
       <c r="D17" t="n">
-        <v>1.15735</v>
+        <v>1.12917</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6158400000000001</v>
+        <v>0.60561</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1286</v>
+        <v>1.12247</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6100100000000001</v>
+        <v>0.61693</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12041</v>
+        <v>1.13045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6119</v>
+        <v>0.61538</v>
       </c>
       <c r="D20" t="n">
-        <v>1.15847</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.62069</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.13088</v>
+        <v>1.10815</v>
       </c>
     </row>
   </sheetData>
